--- a/results/link-prediction-gcn/Link/3shot/PubMed/GCN_total_results.xlsx
+++ b/results/link-prediction-gcn/Link/3shot/PubMed/GCN_total_results.xlsx
@@ -893,457 +893,457 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>0.5930±0.1315</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.4742±0.0297</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.4732±0.0358</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.4994±0.0000</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.5100±0.0000</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.5053±0.0056</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.5365±0.0516</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.5365±0.0516</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.5365±0.0516</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.6086±0.0091</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.5874±0.0651</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0.5049±0.0069</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.6613±0.0000</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.6613±0.0000</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.6613±0.0000</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0.4727±0.0358</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0.4794±0.0288</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.4991±0.0010</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0.4987±0.0008</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.5149±0.0211</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.5586±0.0288</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.5586±0.0288</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.5586±0.0288</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.5745±0.1054</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.6627±0.1037</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0.5493±0.0191</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0.5951±0.0000</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.6701±0.0000</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0.5000±0.0001</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0.5143±0.0120</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0.4398±0.0000</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0.4939±0.0000</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0.4938±0.0000</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.5579±0.0819</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.6889±0.0033</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.6889±0.0033</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.6889±0.0033</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.5490±0.0693</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.6540±0.0492</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.7004±0.0046</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0.4986±0.0020</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.5644±0.0816</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.4892±0.0072</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.5023±0.0338</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AT2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.6678±0.0187</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.6721±0.0167</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.6721±0.0167</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>0.6721±0.0167</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.6488±0.0044</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.6814±0.0060</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.6909±0.0039</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>0.5037±0.0053</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.4671±0.0391</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.5020±0.0014</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0.7067±0.0000</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0.5303±0.0428</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>0.5774±0.0597</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>0.5774±0.0597</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>0.5774±0.0597</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.5018±0.0019</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.6992±0.0277</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>0.6733±0.0192</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>0.5062±0.0088</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0.4977±0.0053</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>0.5147±0.0202</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>0.4844±0.0000</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>0.4999±0.0000</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0.6830±0.0000</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>0.6830±0.0000</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0.6830±0.0000</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>0.6728±0.0000</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>0.6952±0.0000</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0.6230±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.4798±0.0000</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.4843±0.0000</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>0.6213±0.0705</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>0.5059±0.0084</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>0.7085±0.0000</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>0.7098±0.0000</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>0.7098±0.0000</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>0.7098±0.0000</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>0.7005±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0.7145±0.0000</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>0.7165±0.0000</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>0.5859±0.0000</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0.4394±0.0000</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0.4993±0.0000</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>0.6830±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>0.6830±0.0000</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>0.6830±0.0000</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0.7216±0.0000</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>0.7120±0.0000</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>0.4550±0.0000</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>0.4835±0.0000</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>0.5001±0.0000</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5001±0.0002</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0.4874±0.0000</t>
+          <t>0.4559±0.0231</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.4917±0.0000</t>
+          <t>0.4903±0.0513</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.4995±0.0006</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.4988±0.0018</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.5208±0.0000</t>
+          <t>0.5170±0.0097</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.5151±0.0000</t>
+          <t>0.5144±0.0037</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.5151±0.0000</t>
+          <t>0.5144±0.0037</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.5151±0.0000</t>
+          <t>0.5144±0.0037</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>0.5362±0.0000</t>
+          <t>0.5206±0.0070</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>0.5528±0.0000</t>
+          <t>0.5415±0.0249</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>0.5446±0.0000</t>
+          <t>0.5427±0.0067</t>
         </is>
       </c>
     </row>
@@ -1355,457 +1355,457 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>0.7122±0.0644</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.6343±0.0391</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.6197±0.0317</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0.6656±0.0000</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.6426±0.0000</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.6690±0.0025</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.6826±0.0225</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.6826±0.0225</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.6826±0.0225</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.6806±0.0061</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.7055±0.0287</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.4678±0.2813</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.7349±0.0000</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.7349±0.0000</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.7349±0.0000</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0.6264±0.0291</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.6190±0.0103</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.6650±0.0013</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.6648±0.0012</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.6734±0.0095</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.6935±0.0137</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.6935±0.0137</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.6935±0.0137</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.7036±0.0522</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.7484±0.0532</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.6893±0.0089</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0.6506±0.0000</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0.7426±0.0000</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0.6666±0.0001</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0.6633±0.0012</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0.5845±0.0000</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0.5985±0.0000</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0.6602±0.0000</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.6910±0.0344</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.7549±0.0037</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.7549±0.0037</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.7549±0.0037</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0.6893±0.0320</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.7357±0.0276</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.7621±0.0016</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0.6654±0.0018</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.6955±0.0365</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.6540±0.0088</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.6431±0.0259</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0.6666±0.0000</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0.6666±0.0000</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.6666±0.0000</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AT3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.7692±0.0000</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.7440±0.0092</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.7465±0.0074</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.7465±0.0074</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.7465±0.0074</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.7352±0.0030</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.7485±0.0033</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.7544±0.0038</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>0.6683±0.0024</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.6303±0.0445</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.6672±0.0005</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>0.6523±0.0000</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>0.6659±0.0000</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.6809±0.0201</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.7036±0.0288</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.7036±0.0288</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.7036±0.0288</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.6675±0.0009</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.7635±0.0147</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>0.7499±0.0116</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>0.4470±0.3161</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0.6630±0.0050</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>0.6707±0.0054</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0.7512±0.0000</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>0.7512±0.0000</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>0.7512±0.0000</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>0.7424±0.0000</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>0.7581±0.0000</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>0.7195±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.6402±0.0000</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.6466±0.0000</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>0.7606±0.0000</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>0.7653±0.0000</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>0.7653±0.0000</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>0.7653±0.0000</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>0.7583±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.7679±0.0000</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>0.7699±0.0000</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>0.3654±0.0000</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0.6016±0.0000</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0.6654±0.0000</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>0.7551±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>0.7551±0.0000</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>0.7551±0.0000</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.7763±0.0000</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>0.7700±0.0000</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>0.6227±0.0000</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>0.6491±0.0000</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.7207±0.0326</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6693±0.0037</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>0.0000±0.0000</t>
+          <t>0.4444±0.3143</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6667±0.0001</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0.6515±0.0000</t>
+          <t>0.6185±0.0273</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.6570±0.0000</t>
+          <t>0.6226±0.0359</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6655±0.0016</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6649±0.0025</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.6753±0.0000</t>
+          <t>0.6734±0.0039</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.6710±0.0000</t>
+          <t>0.6705±0.0013</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.6710±0.0000</t>
+          <t>0.6705±0.0013</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.6710±0.0000</t>
+          <t>0.6705±0.0013</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0.6814±0.0000</t>
+          <t>0.6749±0.0028</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0.6880±0.0000</t>
+          <t>0.6833±0.0100</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0.6843±0.0000</t>
+          <t>0.6832±0.0022</t>
         </is>
       </c>
     </row>
@@ -1817,457 +1817,457 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.8168±0.0000</t>
+          <t>0.7778±0.0627</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.8899±0.0000</t>
+          <t>0.8716±0.0260</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.5051±0.0000</t>
+          <t>0.6891±0.0080</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.6768±0.0000</t>
+          <t>0.6885±0.0193</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.8866±0.0000</t>
+          <t>0.8958±0.0033</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.8784±0.0000</t>
+          <t>0.9029±0.0148</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.8742±0.0000</t>
+          <t>0.8813±0.0145</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.8064±0.0000</t>
+          <t>0.8597±0.0067</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.8064±0.0000</t>
+          <t>0.8597±0.0067</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.8064±0.0000</t>
+          <t>0.8597±0.0067</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.8629±0.0000</t>
+          <t>0.8782±0.0153</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.6868±0.0000</t>
+          <t>0.7331±0.0035</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.8015±0.0000</t>
+          <t>0.7901±0.0135</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.6477±0.0000</t>
+          <t>0.5203±0.1013</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.8257±0.0000</t>
+          <t>0.8451±0.0358</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.5328±0.0000</t>
+          <t>0.6770±0.0302</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.6467±0.0000</t>
+          <t>0.6673±0.0237</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.7997±0.0000</t>
+          <t>0.8617±0.0089</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.8543±0.0116</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.8954±0.0000</t>
+          <t>0.9150±0.0188</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.6711±0.0000</t>
+          <t>0.9244±0.0021</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.6711±0.0000</t>
+          <t>0.9244±0.0021</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.6711±0.0000</t>
+          <t>0.9244±0.0021</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.9021±0.0000</t>
+          <t>0.8882±0.0320</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.8683±0.0000</t>
+          <t>0.8197±0.0700</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.7631±0.0000</t>
+          <t>0.9165±0.0108</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.7488±0.0000</t>
+          <t>0.7016±0.0563</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.8944±0.0000</t>
+          <t>0.8633±0.0316</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.6731±0.0000</t>
+          <t>0.6888±0.0249</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.7223±0.0000</t>
+          <t>0.7678±0.0211</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.8869±0.0000</t>
+          <t>0.8894±0.0015</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.8910±0.0000</t>
+          <t>0.8986±0.0047</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.8605±0.0000</t>
+          <t>0.8429±0.0294</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.8553±0.0000</t>
+          <t>0.8614±0.0156</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.8553±0.0000</t>
+          <t>0.8614±0.0156</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.8553±0.0000</t>
+          <t>0.8614±0.0156</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.8556±0.0000</t>
+          <t>0.8504±0.0140</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.8278±0.0000</t>
+          <t>0.8360±0.0323</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.8301±0.0000</t>
+          <t>0.8358±0.0089</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.7355±0.0000</t>
+          <t>0.6338±0.1037</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.8424±0.0000</t>
+          <t>0.8697±0.0215</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.4793±0.0000</t>
+          <t>0.7149±0.0396</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.5575±0.0000</t>
+          <t>0.6897±0.0087</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.9036±0.0000</t>
+          <t>0.8888±0.0030</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.8900±0.0000</t>
+          <t>0.8896±0.0052</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.8554±0.0000</t>
+          <t>0.8794±0.0143</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.8787±0.0000</t>
+          <t>0.8696±0.0114</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.8787±0.0000</t>
+          <t>0.8696±0.0114</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.8787±0.0000</t>
+          <t>0.8696±0.0114</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.8623±0.0000</t>
+          <t>0.8842±0.0167</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.8477±0.0000</t>
+          <t>0.8454±0.0041</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.8529±0.0000</t>
+          <t>0.8342±0.0103</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.6404±0.0000</t>
+          <t>0.5961±0.0281</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.8879±0.0000</t>
+          <t>0.8702±0.0274</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.5548±0.0000</t>
+          <t>0.6697±0.0116</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.6908±0.0000</t>
+          <t>0.7172±0.0178</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.8966±0.0000</t>
+          <t>0.8933±0.0013</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.9024±0.0000</t>
+          <t>0.9012±0.0103</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.8771±0.0000</t>
+          <t>0.8851±0.0313</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0.9047±0.0000</t>
+          <t>0.9198±0.0040</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.9047±0.0000</t>
+          <t>0.9198±0.0040</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.9047±0.0000</t>
+          <t>0.9198±0.0040</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.8682±0.0000</t>
+          <t>0.8918±0.0168</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.8745±0.0000</t>
+          <t>0.8720±0.0045</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.8824±0.0000</t>
+          <t>0.8501±0.0220</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.8054±0.0000</t>
+          <t>0.8096±0.0150</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.8976±0.0000</t>
+          <t>0.8941±0.0020</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0.5762±0.0000</t>
+          <t>0.7168±0.0308</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.6888±0.0000</t>
+          <t>0.7162±0.0233</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.8888±0.0000</t>
+          <t>0.8908±0.0024</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.8922±0.0000</t>
+          <t>0.8923±0.0012</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.8954±0.0000</t>
+          <t>0.8859±0.0104</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.8983±0.0000</t>
+          <t>0.8806±0.0166</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.8983±0.0000</t>
+          <t>0.8806±0.0166</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0.8983±0.0000</t>
+          <t>0.8806±0.0166</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.8961±0.0000</t>
+          <t>0.8870±0.0088</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.7079±0.0000</t>
+          <t>0.8388±0.0151</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>0.8608±0.0000</t>
+          <t>0.8386±0.0218</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.2084±0.0000</t>
+          <t>0.5411±0.2539</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.9063±0.0000</t>
+          <t>0.8913±0.0096</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.4877±0.0000</t>
+          <t>0.5979±0.0969</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.4917±0.0000</t>
+          <t>0.5805±0.0708</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.7643±0.0000</t>
+          <t>0.8681±0.0064</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.8183±0.0000</t>
+          <t>0.8658±0.0178</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.8680±0.0000</t>
+          <t>0.8529±0.0099</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.7478±0.0000</t>
+          <t>0.7360±0.0171</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.7478±0.0000</t>
+          <t>0.7360±0.0171</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.7478±0.0000</t>
+          <t>0.7360±0.0171</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>0.8457±0.0000</t>
+          <t>0.8513±0.0115</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>0.7503±0.0000</t>
+          <t>0.7528±0.0056</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>0.7024±0.0000</t>
+          <t>0.6891±0.0098</t>
         </is>
       </c>
     </row>
@@ -2279,457 +2279,457 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.7716±0.0000</t>
+          <t>0.7503±0.0463</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.8754±0.0000</t>
+          <t>0.8570±0.0194</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.5026±0.0000</t>
+          <t>0.7527±0.0128</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.6869±0.0000</t>
+          <t>0.7423±0.0296</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.8707±0.0000</t>
+          <t>0.8815±0.0043</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.8634±0.0000</t>
+          <t>0.8894±0.0156</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.8661±0.0000</t>
+          <t>0.8662±0.0102</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.8126±0.0000</t>
+          <t>0.8533±0.0042</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.8126±0.0000</t>
+          <t>0.8533±0.0042</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.8126±0.0000</t>
+          <t>0.8533±0.0042</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.8594±0.0000</t>
+          <t>0.8638±0.0107</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.7213±0.0000</t>
+          <t>0.7616±0.0034</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.8001±0.0000</t>
+          <t>0.7910±0.0121</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.6882±0.0000</t>
+          <t>0.6142±0.0662</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.8381±0.0000</t>
+          <t>0.8420±0.0274</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.5322±0.0000</t>
+          <t>0.6825±0.0192</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.6615±0.0000</t>
+          <t>0.6911±0.0262</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.8318±0.0000</t>
+          <t>0.8515±0.0047</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.8562±0.0058</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.8992±0.0000</t>
+          <t>0.9091±0.0167</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.7411±0.0000</t>
+          <t>0.9116±0.0019</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7411±0.0000</t>
+          <t>0.9116±0.0019</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.7411±0.0000</t>
+          <t>0.9116±0.0019</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.9069±0.0000</t>
+          <t>0.8839±0.0310</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.8277±0.0000</t>
+          <t>0.7745±0.0793</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.7770±0.0000</t>
+          <t>0.9042±0.0108</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.7287±0.0000</t>
+          <t>0.7148±0.0262</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.8777±0.0000</t>
+          <t>0.8510±0.0220</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.7345±0.0000</t>
+          <t>0.7213±0.0364</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.7804±0.0000</t>
+          <t>0.8036±0.0096</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.8712±0.0000</t>
+          <t>0.8748±0.0023</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.8726±0.0000</t>
+          <t>0.8849±0.0094</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.8617±0.0000</t>
+          <t>0.8456±0.0157</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.8678±0.0000</t>
+          <t>0.8627±0.0141</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.8678±0.0000</t>
+          <t>0.8627±0.0141</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.8678±0.0000</t>
+          <t>0.8627±0.0141</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.8592±0.0000</t>
+          <t>0.8494±0.0099</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.8202±0.0000</t>
+          <t>0.8307±0.0299</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.8215±0.0000</t>
+          <t>0.8306±0.0127</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.7308±0.0000</t>
+          <t>0.6787±0.0622</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.8595±0.0000</t>
+          <t>0.8693±0.0141</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.4899±0.0000</t>
+          <t>0.7446±0.0344</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.5367±0.0000</t>
+          <t>0.7006±0.0279</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.8888±0.0000</t>
+          <t>0.8761±0.0056</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.8787±0.0000</t>
+          <t>0.8775±0.0056</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.8670±0.0000</t>
+          <t>0.8848±0.0114</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.8862±0.0000</t>
+          <t>0.8745±0.0112</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.8862±0.0000</t>
+          <t>0.8745±0.0112</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.8862±0.0000</t>
+          <t>0.8745±0.0112</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.8718±0.0000</t>
+          <t>0.8876±0.0124</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.8356±0.0000</t>
+          <t>0.8354±0.0071</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.8482±0.0000</t>
+          <t>0.8336±0.0129</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.6775±0.0000</t>
+          <t>0.6598±0.0212</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.8745±0.0000</t>
+          <t>0.8587±0.0162</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.5524±0.0000</t>
+          <t>0.7322±0.0282</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.6981±0.0000</t>
+          <t>0.7361±0.0127</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.8805±0.0000</t>
+          <t>0.8789±0.0011</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.8847±0.0000</t>
+          <t>0.8904±0.0090</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.8687±0.0000</t>
+          <t>0.8767±0.0280</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.9062±0.0000</t>
+          <t>0.9122±0.0050</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.9062±0.0000</t>
+          <t>0.9122±0.0050</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.9062±0.0000</t>
+          <t>0.9122±0.0050</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.8627±0.0000</t>
+          <t>0.8821±0.0153</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.8485±0.0000</t>
+          <t>0.8490±0.0068</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.8839±0.0000</t>
+          <t>0.8462±0.0234</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.7785±0.0000</t>
+          <t>0.7738±0.0165</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.8770±0.0000</t>
+          <t>0.8672±0.0053</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.5931±0.0000</t>
+          <t>0.7386±0.0428</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.7548±0.0000</t>
+          <t>0.7431±0.0375</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.8711±0.0000</t>
+          <t>0.8754±0.0030</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.8734±0.0000</t>
+          <t>0.8752±0.0021</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.8767±0.0000</t>
+          <t>0.8648±0.0096</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.8786±0.0000</t>
+          <t>0.8625±0.0136</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.8786±0.0000</t>
+          <t>0.8625±0.0136</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.8786±0.0000</t>
+          <t>0.8625±0.0136</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.8775±0.0000</t>
+          <t>0.8662±0.0084</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.7469±0.0000</t>
+          <t>0.8536±0.0082</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.8467±0.0000</t>
+          <t>0.8246±0.0165</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.3468±0.0000</t>
+          <t>0.5880±0.1771</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.8861±0.0000</t>
+          <t>0.8757±0.0058</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.4939±0.0000</t>
+          <t>0.6063±0.1021</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.4959±0.0000</t>
+          <t>0.5764±0.0600</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.7002±0.0000</t>
+          <t>0.8557±0.0076</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.8389±0.0000</t>
+          <t>0.8638±0.0099</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.8578±0.0000</t>
+          <t>0.8461±0.0076</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.7179±0.0000</t>
+          <t>0.6834±0.0257</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.7179±0.0000</t>
+          <t>0.6834±0.0257</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.7179±0.0000</t>
+          <t>0.6834±0.0257</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>0.8429±0.0000</t>
+          <t>0.8444±0.0091</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>0.7211±0.0000</t>
+          <t>0.7270±0.0056</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>0.6579±0.0000</t>
+          <t>0.6347±0.0141</t>
         </is>
       </c>
     </row>
